--- a/artfynd/A 37408-2022 artfynd.xlsx
+++ b/artfynd/A 37408-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37408-2022 artfynd.xlsx
+++ b/artfynd/A 37408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>66538135</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>390166.2450746756</v>
+        <v>390166</v>
       </c>
       <c r="R2" t="n">
-        <v>6613354.649239701</v>
+        <v>6613355</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2012-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -794,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>66538143</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnkullen NV, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>390154</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6613383</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-05-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>20988</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
